--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0005.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0005.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Dấu Vết Núi Firmament</t>
+          <t>Dấu Vết Mt. Firmament</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Đạt kỷ lục mới trong Đánh Giá Điều Ước có thể tăng Độ Nổi Tiếng. Increase chỉ số Companions để có Đánh Giá Điều Ước cao hơn.</t>
+          <t>Đạt kỷ lục mới trong Đánh Giá Điều Ước có thể tăng Độ Nổi Tiếng. Tăng chỉ số Companions để có Đánh Giá Điều Ước cao hơn.</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -15136,7 +15136,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Rương Cung Cấp</t>
+          <t>Supply Chest</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Điểm Dị Thường New: Discord đã mở khóa</t>
+          <t>Điểm Dị Thường New: Tacet Discord đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -18516,7 +18516,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
     </row>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -26188,7 +26188,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -26773,7 +26773,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -27423,7 +27423,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Claimable sau khi mời tất cả Companions</t>
+          <t>Có thể nhận sau khi mời tất cả Companions</t>
         </is>
       </c>
     </row>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -30673,7 +30673,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Mới</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Mới</t>
         </is>
       </c>
     </row>
@@ -32038,7 +32038,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -32558,7 +32558,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
